--- a/deliverables/otb-diagnosis/tagging-template.xlsx
+++ b/deliverables/otb-diagnosis/tagging-template.xlsx
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="H6" s="7">
-        <f>COUNTIF(D2:D21,"?")</f>
+        <f>COUNTIF(D2:D21,"~?")</f>
         <v/>
       </c>
     </row>
